--- a/public/documents/pieces-reponse-1/R1-releve-reponses-service.xlsx
+++ b/public/documents/pieces-reponse-1/R1-releve-reponses-service.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,6 +41,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="4">
@@ -87,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -98,6 +102,10 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -466,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -487,7 +495,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Une ligne par rubrique du courrier. La derniere colonne est la seule qui compte dans un bilan matiere : le service dit-il, pour ce poste, combien de litres sont reellement partis ? Chaque ligne porte sa page : le releve est verifiable.</t>
+          <t>Une ligne par rubrique du courrier. La colonne « Volume mesure oppose ? » est la seule qui compte dans un bilan matiere : le service dit-il, pour ce poste, combien de litres sont reellement partis, releve a l'appui ? Le courrier cite bien des litres, et le troisieme bloc ci-dessous les aligne un a un : ils sont tous produits par ses propres taux ou par ses propres colonnes. Chaque ligne porte sa page : le releve est verifiable.</t>
         </is>
       </c>
     </row>
@@ -514,7 +522,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Volume alternatif oppose ?</t>
+          <t>Volume mesure oppose ?</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -1171,7 +1179,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>20 rubriques</t>
+          <t>20 lignes relevees</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr"/>
@@ -1182,10 +1190,426 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>non : 18 sur 20</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr"/>
+          <t>non : 18 sur 19</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>20 lignes relevees, dont 1 repere sans rubrique « Reponse du service » (L, chapeau de la page 59) : le denominateur est donc de 19 rubriques, dont 1 concession (point 10), sans objet au regard d'un volume.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Ce que le service CITE, et ce qu'il MESURE : les volumes ecrits dans le courrier, un a un</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Le courrier n'est pas muet en litres. Il en ecrit dix, pour un total de 2 132,01 L. Aucun n'est un volume mesure dans le poste auquel il est oppose : chacun est le produit d'un taux forfaitaire du service ou la lecture d'une de ses propres colonnes. C'est la distinction que porte la colonne « Volume mesure oppose ? » de l'onglet ci-dessus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Volume cite</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Page(s)</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Rubrique du courrier</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>D'ou vient ce chiffre</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Volume mesure dans le poste ?</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Pourquoi ce n'est pas une mesure</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>198 L</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Point 4, dégustation offerte</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Son taux de 15 % offert/perte/personnel appliqué aux BIB</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Produit d'un forfait de sa propre méthode, appliqué à un volume d'achat. Ne dit rien du nombre de dégustations réellement servies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>500 L</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Point 4, dégustation offerte</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Le même taux de 15 % appliqué aux bouteilles</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>« environ 500 litres » au courrier : chiffre arrondi par le service lui-même, et produit du même forfait.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>93 L</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>68 à 70</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Point 6, alcool cuit dans les plats des menus</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Repère D, Calvados déjà retranché par sa méthode</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>Retranchement que le service opère déjà dans sa reconstitution : c'est son propre chiffre, repris pour soutenir un double emploi, non une mesure de l'alcool cuit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>111 L</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>68 à 70</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Point 6, alcool cuit dans les plats des menus</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Repère E, vin jaune déjà retranché par sa méthode</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>Idem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>15 L</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>68 à 70</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Point 6, alcool cuit dans les plats des menus</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>Repère G, porto déjà retranché par sa méthode</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>Idem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>240 L</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>68 à 70</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Point 6, alcool cuit dans les plats des menus</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Repère Q, macvin déjà retranché par sa méthode</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>Idem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>796,43 L</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>68 à 70</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Point 6, alcool cuit dans les plats des menus</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>Volume unique des BIB porté par sa propre colonne</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>Volume d'achat lu dans sa propre colonne, non un volume cuisiné.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>33,28 L</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>68 à 70</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Point 6, alcool cuit dans les plats des menus</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>Crèmes, même colonne</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>Idem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>83,84 L</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>70 et 71</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Point 7, consommation du personnel</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>5 % de son propre volume de référence</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>« 5 % de ce volume correspondent donc à 83,84 litres » : le produit d'un forfait, non un relevé de ce que le personnel a consommé.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>61,46 L</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>70 et 71</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Point 7, consommation du personnel</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>Le même forfait de 5 % sur l'autre assiette</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>Idem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>2 132,01 L</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>p. 64 a 71</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>10 volumes cites</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Taux forfaitaires et colonnes du service</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>Total des volumes ecrits par le courrier sur le bloc reconstitution. Le releve ne soutient donc pas que le service ne cite aucun litre : il soutient qu'aucun de ces litres ne mesure ce qui est reellement parti dans le poste, et qu'aucun n'est donc opposable comme volume.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>Deux volumes cites au point 3 (cremant, p. 62 et 63), 93,20 L et 206,25 L, ne figurent pas dans cette addition : ce sont les chiffres de la societe, que le service reprend pour un calcul de coherence (45,18 % de pertes), non des volumes qu'il oppose au poste. Ils sont rapportes tels quels a la ligne 3 de l'onglet ci-dessus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>Lecture d'ensemble. Sur les 19 rubriques « Reponse du service » du bloc, 18 n'opposent aucun volume mesure au poste discute ; la derniere est une concession (point 10, ventes sans achat), sans objet au regard d'un volume. Le repere L, chapeau de la page 59, ne comporte pas de rubrique et ne compte donc pas au denominateur, ce qui porte le releve a 20 lignes.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1261,15 +1685,15 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>pages 60 a 89</t>
         </is>
